--- a/branches/fix/java-validation-output/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
+++ b/branches/fix/java-validation-output/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:44:04+00:00</t>
+    <t>2026-09-14T12:02:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/java-validation-output/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
+++ b/branches/fix/java-validation-output/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:02:11+00:00</t>
+    <t>2026-09-14T12:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
